--- a/artfynd/Aspmyrbäcken artfynd.xlsx
+++ b/artfynd/Aspmyrbäcken artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73342844</v>
+        <v>7125456</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665942</v>
+        <v>665231</v>
       </c>
       <c r="R2" t="n">
-        <v>7133103</v>
+        <v>7134896</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2011-08-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2011-08-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29495</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73342845</v>
+        <v>7125770</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +792,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666405</v>
+        <v>665326</v>
       </c>
       <c r="R3" t="n">
-        <v>7133560</v>
+        <v>7134888</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2011-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2011-07-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29514</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,72 +875,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73342853</v>
+        <v>520366</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Mossavattenberget, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667302</v>
+        <v>665816</v>
       </c>
       <c r="R4" t="n">
-        <v>7133652</v>
+        <v>7132871</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -946,12 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2004-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2004-09-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,22 +972,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73342855</v>
+        <v>7125457</v>
       </c>
       <c r="B5" t="n">
-        <v>88654</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,37 +995,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667292</v>
+        <v>665351</v>
       </c>
       <c r="R5" t="n">
-        <v>7133349</v>
+        <v>7135343</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1043,12 +1053,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2011-08-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2011-08-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29496</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,60 +1078,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73342723</v>
+        <v>7126071</v>
       </c>
       <c r="B6" t="n">
-        <v>91699</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Flakaträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666357</v>
+        <v>666330</v>
       </c>
       <c r="R6" t="n">
-        <v>7133367</v>
+        <v>7131902</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1140,12 +1159,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2011-08-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2011-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29488</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,44 +1184,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73342717</v>
+        <v>73342844</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1207,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666370</v>
+        <v>665942</v>
       </c>
       <c r="R7" t="n">
-        <v>7133399</v>
+        <v>7133103</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,32 +1293,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73342712</v>
+        <v>73342846</v>
       </c>
       <c r="B8" t="n">
-        <v>91263</v>
+        <v>92123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>666587</v>
+        <v>666410</v>
       </c>
       <c r="R8" t="n">
-        <v>7133222</v>
+        <v>7133567</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7126071</v>
+        <v>73342720</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>89292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,41 +1401,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flakaträsk, Ly lm</t>
+          <t>Mossavattenberget norra, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666330</v>
+        <v>666370</v>
       </c>
       <c r="R9" t="n">
-        <v>7131902</v>
+        <v>7133399</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,17 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-08-02</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-08-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29488</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1460,12 +1475,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1475,7 +1490,7 @@
         <v>73342847</v>
       </c>
       <c r="B10" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,12 +1507,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73342806</v>
+        <v>73342717</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1604,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666624</v>
+        <v>666370</v>
       </c>
       <c r="R11" t="n">
-        <v>7133203</v>
+        <v>7133399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,10 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73342716</v>
+        <v>73342726</v>
       </c>
       <c r="B12" t="n">
-        <v>80084</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1677,21 +1692,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1701,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666440</v>
+        <v>666229</v>
       </c>
       <c r="R12" t="n">
-        <v>7133437</v>
+        <v>7133301</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1760,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1764,32 +1778,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73342728</v>
+        <v>73342845</v>
       </c>
       <c r="B13" t="n">
-        <v>79987</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1799,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666192</v>
+        <v>666405</v>
       </c>
       <c r="R13" t="n">
-        <v>7133300</v>
+        <v>7133560</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73342854</v>
+        <v>73342719</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1872,21 +1886,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1896,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667326</v>
+        <v>666370</v>
       </c>
       <c r="R14" t="n">
-        <v>7133356</v>
+        <v>7133399</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>73342721</v>
+        <v>73342723</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1969,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>73342851</v>
+        <v>73342725</v>
       </c>
       <c r="B16" t="n">
-        <v>91263</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2066,21 +2080,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2090,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>667134</v>
+        <v>666229</v>
       </c>
       <c r="R16" t="n">
-        <v>7133680</v>
+        <v>7133301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,32 +2166,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>73342805</v>
+        <v>73342716</v>
       </c>
       <c r="B17" t="n">
-        <v>80112</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666749</v>
+        <v>666440</v>
       </c>
       <c r="R17" t="n">
-        <v>7133210</v>
+        <v>7133437</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,6 +2245,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2249,10 +2264,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73342797</v>
+        <v>73342729</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2260,21 +2275,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2284,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666908</v>
+        <v>666085</v>
       </c>
       <c r="R18" t="n">
-        <v>7133259</v>
+        <v>7133256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2346,10 +2361,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>73342786</v>
+        <v>127414873</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,34 +2372,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>667084</v>
+        <v>666212</v>
       </c>
       <c r="R19" t="n">
-        <v>7133272</v>
+        <v>7134086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2411,12 +2430,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2431,44 +2455,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>73342720</v>
+        <v>73342721</v>
       </c>
       <c r="B20" t="n">
-        <v>88654</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2478,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>666370</v>
+        <v>666357</v>
       </c>
       <c r="R20" t="n">
-        <v>7133399</v>
+        <v>7133367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2540,32 +2564,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>73342848</v>
+        <v>73342724</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>80336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2575,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>666495</v>
+        <v>666297</v>
       </c>
       <c r="R21" t="n">
-        <v>7133719</v>
+        <v>7133333</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2637,52 +2661,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7125770</v>
+        <v>73342728</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granträsk, Ly lm</t>
+          <t>Mossavattenberget norra, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665326</v>
+        <v>666192</v>
       </c>
       <c r="R22" t="n">
-        <v>7134888</v>
+        <v>7133300</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2706,17 +2726,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2011-07-19</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2011-07-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29514</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2731,22 +2746,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>73342793</v>
+        <v>73342715</v>
       </c>
       <c r="B23" t="n">
-        <v>88654</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2754,21 +2769,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2778,10 +2793,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666984</v>
+        <v>666440</v>
       </c>
       <c r="R23" t="n">
-        <v>7133234</v>
+        <v>7133437</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2840,10 +2855,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>73342718</v>
+        <v>73342727</v>
       </c>
       <c r="B24" t="n">
-        <v>91263</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2866,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2890,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666370</v>
+        <v>666192</v>
       </c>
       <c r="R24" t="n">
-        <v>7133399</v>
+        <v>7133300</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2937,10 +2952,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>73342783</v>
+        <v>73342730</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2972,10 +2987,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667054</v>
+        <v>666085</v>
       </c>
       <c r="R25" t="n">
-        <v>7133254</v>
+        <v>7133256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3034,45 +3049,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>73342785</v>
+        <v>127414872</v>
       </c>
       <c r="B26" t="n">
-        <v>79987</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667080</v>
+        <v>666207</v>
       </c>
       <c r="R26" t="n">
-        <v>7133253</v>
+        <v>7134017</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3099,12 +3118,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3119,60 +3143,64 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>520366</v>
+        <v>129001120</v>
       </c>
       <c r="B27" t="n">
-        <v>91614</v>
+        <v>92208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1506</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mossavattenberget, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665816</v>
+        <v>666074</v>
       </c>
       <c r="R27" t="n">
-        <v>7132871</v>
+        <v>7134465</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3196,12 +3224,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2004-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2004-09-27</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3216,22 +3249,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7125457</v>
+        <v>129001126</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>92208</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3272,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3267,13 +3300,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665351</v>
+        <v>666030</v>
       </c>
       <c r="R28" t="n">
-        <v>7135343</v>
+        <v>7134585</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3297,17 +3330,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2011-08-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2011-08-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29496</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3322,57 +3355,61 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>73342800</v>
+        <v>129001128</v>
       </c>
       <c r="B29" t="n">
-        <v>91446</v>
+        <v>92208</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>666840</v>
+        <v>666057</v>
       </c>
       <c r="R29" t="n">
-        <v>7133206</v>
+        <v>7134506</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3399,12 +3436,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3419,57 +3461,61 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>73342724</v>
+        <v>129001121</v>
       </c>
       <c r="B30" t="n">
-        <v>79987</v>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>666297</v>
+        <v>666072</v>
       </c>
       <c r="R30" t="n">
-        <v>7133333</v>
+        <v>7134463</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3496,12 +3542,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3516,57 +3567,61 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>73342846</v>
+        <v>129001125</v>
       </c>
       <c r="B31" t="n">
-        <v>91446</v>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>666410</v>
+        <v>666030</v>
       </c>
       <c r="R31" t="n">
-        <v>7133567</v>
+        <v>7134586</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3593,12 +3648,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3613,22 +3673,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>73342801</v>
+        <v>129001129</v>
       </c>
       <c r="B32" t="n">
-        <v>91420</v>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3636,34 +3696,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>666819</v>
+        <v>666059</v>
       </c>
       <c r="R32" t="n">
-        <v>7133209</v>
+        <v>7134504</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3690,12 +3754,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3710,26 +3779,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>73342725</v>
+        <v>129001118</v>
       </c>
       <c r="B33" t="n">
-        <v>91699</v>
+        <v>92369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3742,25 +3811,29 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>666229</v>
+        <v>666072</v>
       </c>
       <c r="R33" t="n">
-        <v>7133301</v>
+        <v>7134463</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3787,12 +3860,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3807,57 +3885,61 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>73342857</v>
+        <v>129001130</v>
       </c>
       <c r="B34" t="n">
-        <v>91446</v>
+        <v>92369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>667284</v>
+        <v>666041</v>
       </c>
       <c r="R34" t="n">
-        <v>7133334</v>
+        <v>7134497</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3884,12 +3966,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3904,22 +3991,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>73342798</v>
+        <v>129001123</v>
       </c>
       <c r="B35" t="n">
-        <v>91245</v>
+        <v>83173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3927,34 +4014,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>666908</v>
+        <v>666056</v>
       </c>
       <c r="R35" t="n">
-        <v>7133259</v>
+        <v>7134573</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3981,12 +4072,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4001,57 +4097,61 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>73342711</v>
+        <v>129001114</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>92632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>666587</v>
+        <v>666116</v>
       </c>
       <c r="R36" t="n">
-        <v>7133222</v>
+        <v>7134265</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4078,12 +4178,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4098,57 +4203,61 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>73342807</v>
+        <v>129001122</v>
       </c>
       <c r="B37" t="n">
-        <v>91541</v>
+        <v>91872</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>666624</v>
+        <v>666074</v>
       </c>
       <c r="R37" t="n">
-        <v>7133203</v>
+        <v>7134460</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4175,12 +4284,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4195,57 +4309,61 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>73342726</v>
+        <v>129001127</v>
       </c>
       <c r="B38" t="n">
-        <v>91245</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>666229</v>
+        <v>665992</v>
       </c>
       <c r="R38" t="n">
-        <v>7133301</v>
+        <v>7134641</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4272,12 +4390,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4292,22 +4415,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>73342730</v>
+        <v>127414874</v>
       </c>
       <c r="B39" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4332,17 +4455,21 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>666085</v>
+        <v>666165</v>
       </c>
       <c r="R39" t="n">
-        <v>7133256</v>
+        <v>7134261</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4369,12 +4496,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4389,57 +4521,61 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>73342795</v>
+        <v>127414875</v>
       </c>
       <c r="B40" t="n">
-        <v>91245</v>
+        <v>80461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>666969</v>
+        <v>666059</v>
       </c>
       <c r="R40" t="n">
-        <v>7133236</v>
+        <v>7134408</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4466,12 +4602,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4486,57 +4627,61 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>73342719</v>
+        <v>127414877</v>
       </c>
       <c r="B41" t="n">
-        <v>91699</v>
+        <v>99035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mossavattenberget norra, Ly lm</t>
+          <t>Granträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>666370</v>
+        <v>666044</v>
       </c>
       <c r="R41" t="n">
-        <v>7133399</v>
+        <v>7134494</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4563,12 +4708,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4583,44 +4733,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>73342803</v>
+        <v>73342800</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>92123</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4630,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>666799</v>
+        <v>666840</v>
       </c>
       <c r="R42" t="n">
-        <v>7133209</v>
+        <v>7133206</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4692,10 +4842,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>73342792</v>
+        <v>73342793</v>
       </c>
       <c r="B43" t="n">
-        <v>80083</v>
+        <v>89292</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4703,21 +4853,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4789,10 +4939,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>73342715</v>
+        <v>73342802</v>
       </c>
       <c r="B44" t="n">
-        <v>80083</v>
+        <v>92208</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4800,21 +4950,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4824,10 +4974,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>666440</v>
+        <v>666819</v>
       </c>
       <c r="R44" t="n">
-        <v>7133437</v>
+        <v>7133209</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4886,10 +5036,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>73342790</v>
+        <v>73342807</v>
       </c>
       <c r="B45" t="n">
-        <v>80084</v>
+        <v>92208</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4897,21 +5047,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4921,10 +5071,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>666969</v>
+        <v>666624</v>
       </c>
       <c r="R45" t="n">
-        <v>7133305</v>
+        <v>7133203</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4983,10 +5133,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>73342727</v>
+        <v>73342801</v>
       </c>
       <c r="B46" t="n">
-        <v>80083</v>
+        <v>92097</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4994,21 +5144,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5018,10 +5168,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>666192</v>
+        <v>666819</v>
       </c>
       <c r="R46" t="n">
-        <v>7133300</v>
+        <v>7133209</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5080,52 +5230,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7125456</v>
+        <v>73342791</v>
       </c>
       <c r="B47" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Granträsk, Ly lm</t>
+          <t>Mossavattenberget norra, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665231</v>
+        <v>666984</v>
       </c>
       <c r="R47" t="n">
-        <v>7134896</v>
+        <v>7133234</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5149,17 +5295,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2011-08-03</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2011-08-03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29495</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5174,44 +5315,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>73342796</v>
+        <v>73342803</v>
       </c>
       <c r="B48" t="n">
-        <v>91263</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5221,10 +5362,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>666933</v>
+        <v>666799</v>
       </c>
       <c r="R48" t="n">
-        <v>7133249</v>
+        <v>7133209</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5283,32 +5424,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>73342729</v>
+        <v>73342806</v>
       </c>
       <c r="B49" t="n">
-        <v>80084</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5318,10 +5459,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>666085</v>
+        <v>666624</v>
       </c>
       <c r="R49" t="n">
-        <v>7133256</v>
+        <v>7133203</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5380,10 +5521,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>73342791</v>
+        <v>73342711</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5391,21 +5532,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5415,10 +5556,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>666984</v>
+        <v>666587</v>
       </c>
       <c r="R50" t="n">
-        <v>7133234</v>
+        <v>7133222</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5477,10 +5618,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>73342788</v>
+        <v>73342792</v>
       </c>
       <c r="B51" t="n">
-        <v>80084</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5488,21 +5629,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5512,10 +5653,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>667084</v>
+        <v>666984</v>
       </c>
       <c r="R51" t="n">
-        <v>7133272</v>
+        <v>7133234</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5574,10 +5715,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>73342849</v>
+        <v>73342805</v>
       </c>
       <c r="B52" t="n">
-        <v>91942</v>
+        <v>80461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5585,21 +5726,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5609,10 +5750,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>666495</v>
+        <v>666749</v>
       </c>
       <c r="R52" t="n">
-        <v>7133719</v>
+        <v>7133210</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5671,10 +5812,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>73342852</v>
+        <v>73342799</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>92208</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5682,21 +5823,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5706,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667295</v>
+        <v>666908</v>
       </c>
       <c r="R53" t="n">
-        <v>7133725</v>
+        <v>7133259</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5768,32 +5909,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>73342850</v>
+        <v>73342795</v>
       </c>
       <c r="B54" t="n">
-        <v>96487</v>
+        <v>91909</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5803,10 +5944,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>666897</v>
+        <v>666969</v>
       </c>
       <c r="R54" t="n">
-        <v>7133616</v>
+        <v>7133236</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5865,10 +6006,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>73342802</v>
+        <v>73342798</v>
       </c>
       <c r="B55" t="n">
-        <v>91541</v>
+        <v>91909</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5876,21 +6017,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5900,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>666819</v>
+        <v>666908</v>
       </c>
       <c r="R55" t="n">
-        <v>7133209</v>
+        <v>7133259</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5962,32 +6103,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>73342843</v>
+        <v>73342714</v>
       </c>
       <c r="B56" t="n">
-        <v>91263</v>
+        <v>92292</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5997,10 +6138,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665899</v>
+        <v>666517</v>
       </c>
       <c r="R56" t="n">
-        <v>7133081</v>
+        <v>7133384</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6059,10 +6200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>73342787</v>
+        <v>73342790</v>
       </c>
       <c r="B57" t="n">
-        <v>80083</v>
+        <v>80433</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6070,21 +6211,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6094,10 +6235,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>667084</v>
+        <v>666969</v>
       </c>
       <c r="R57" t="n">
-        <v>7133272</v>
+        <v>7133305</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6156,32 +6297,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>73342714</v>
+        <v>73342850</v>
       </c>
       <c r="B58" t="n">
-        <v>91614</v>
+        <v>97231</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1506</v>
+        <v>2869</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6191,10 +6332,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>666517</v>
+        <v>666897</v>
       </c>
       <c r="R58" t="n">
-        <v>7133384</v>
+        <v>7133616</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6253,32 +6394,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>73342856</v>
+        <v>73342849</v>
       </c>
       <c r="B59" t="n">
-        <v>91245</v>
+        <v>92632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6288,10 +6429,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>667284</v>
+        <v>666495</v>
       </c>
       <c r="R59" t="n">
-        <v>7133334</v>
+        <v>7133719</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6350,32 +6491,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>73342789</v>
+        <v>73342797</v>
       </c>
       <c r="B60" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6385,10 +6526,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>666969</v>
+        <v>666908</v>
       </c>
       <c r="R60" t="n">
-        <v>7133305</v>
+        <v>7133259</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6447,32 +6588,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>73342799</v>
+        <v>73342848</v>
       </c>
       <c r="B61" t="n">
-        <v>91541</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6482,10 +6623,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>666908</v>
+        <v>666495</v>
       </c>
       <c r="R61" t="n">
-        <v>7133259</v>
+        <v>7133719</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6544,10 +6685,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>73342692</v>
+        <v>73342789</v>
       </c>
       <c r="B62" t="n">
-        <v>91263</v>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6555,21 +6696,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6579,10 +6720,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>666085</v>
+        <v>666969</v>
       </c>
       <c r="R62" t="n">
-        <v>7133256</v>
+        <v>7133305</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6638,6 +6779,1085 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>73342857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92123</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>48</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>667284</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7133334</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>73342855</v>
+      </c>
+      <c r="B64" t="n">
+        <v>89292</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>510</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>667292</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7133349</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>73342856</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>667284</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7133334</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>73342788</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>667084</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7133272</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>73342786</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>667084</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7133272</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>73342852</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>667295</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7133725</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>73342854</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>667326</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7133356</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>73342785</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>667080</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7133253</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>73342783</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>667054</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7133254</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>73342787</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>667084</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7133272</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>73342853</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Mossavattenberget norra, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>667302</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7133652</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2018-09-20</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
